--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484227_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484227_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1332</v>
+        <v>2.3655</v>
       </c>
       <c r="E2" t="n">
-        <v>4.271</v>
+        <v>3.3204</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1378</v>
+        <v>-0.9549</v>
       </c>
       <c r="G2" t="n">
         <v>5.8174</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6754</v>
+        <v>-0.0922</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0677</v>
+        <v>0.1171</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6077</v>
+        <v>-0.2093</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8201000000000001</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>M. DIALLO BADJI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0357</v>
+        <v>1.2432</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0227</v>
+        <v>1.5318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.013</v>
+        <v>-0.2886</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5022</v>
+        <v>0.3664</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4129</v>
+        <v>-0.1867</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9151</v>
+        <v>0.5531</v>
       </c>
       <c r="J3" t="n">
-        <v>1.317</v>
+        <v>0.6005</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0589</v>
+        <v>0.4515</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3758</v>
+        <v>0.149</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1852</v>
+        <v>-0.2342</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.354</v>
+        <v>-0.6382</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5393</v>
+        <v>0.4041</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3907</v>
+        <v>2.5395</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4122</v>
+        <v>-0.8309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8778</v>
+        <v>-0.092</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4656</v>
+        <v>-0.7389</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.488</v>
+        <v>-0.8317</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.488</v>
+        <v>-2.0503</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIALLO BADJI</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7734</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8041</v>
+        <v>0.6788</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.098</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3664</v>
+        <v>1.5022</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1867</v>
+        <v>-0.4129</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5531</v>
+        <v>1.9151</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6005</v>
+        <v>1.317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4515</v>
+        <v>-0.0589</v>
       </c>
       <c r="L4" t="n">
-        <v>0.149</v>
+        <v>1.3758</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2342</v>
+        <v>0.1852</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6382</v>
+        <v>-0.354</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4041</v>
+        <v>0.5393</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5395</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7348</v>
+        <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.368</v>
+        <v>0.15</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8198</v>
+        <v>0.5339</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5483</v>
+        <v>-0.3839</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8317</v>
+        <v>-0.488</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0503</v>
+        <v>-0.488</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.327</v>
+        <v>0.7259</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.517</v>
+        <v>-0.2543</v>
       </c>
       <c r="F5" t="n">
-        <v>0.844</v>
+        <v>0.9802</v>
       </c>
       <c r="G5" t="n">
         <v>0.1619</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8116</v>
+        <v>-0.4127</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4842</v>
+        <v>-0.2214</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3275</v>
+        <v>-0.1913</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. VAN ZUUREN ABAD</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3053</v>
+        <v>-0.405</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4838</v>
+        <v>-2.0954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1785</v>
+        <v>1.6904</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.8716</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1192</v>
+        <v>-1.825</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4992</v>
+        <v>3.6966</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0609</v>
+        <v>2.4551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0205</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>3.0231</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6793</v>
+        <v>-0.5836</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1397</v>
+        <v>-1.2571</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5397</v>
+        <v>0.6735</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-4.1022</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>2.7348</v>
       </c>
       <c r="S7" t="n">
-        <v>0.235</v>
+        <v>-1.3509</v>
       </c>
       <c r="T7" t="n">
-        <v>0.432</v>
+        <v>-0.4483</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.197</v>
+        <v>-0.9026</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6642</v>
+        <v>0.4418</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6642</v>
+        <v>0.4418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>M. VAN ZUUREN ABAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6557</v>
+        <v>-0.6008</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9648</v>
+        <v>-0.8882</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3091</v>
+        <v>0.2874</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8716</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.825</v>
+        <v>-0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6966</v>
+        <v>-0.4992</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4551</v>
+        <v>0.0609</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5679999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
-        <v>3.0231</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5836</v>
+        <v>-0.6793</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2571</v>
+        <v>-0.1397</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6735</v>
+        <v>-0.5397</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1022</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7348</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6016</v>
+        <v>-0.0605</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3177</v>
+        <v>0.0275</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2839</v>
+        <v>-0.0881</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4418</v>
+        <v>0.6642</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4418</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.442</v>
+        <v>-2.0315</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2431</v>
+        <v>0.2219</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1989</v>
+        <v>-2.2534</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3902</v>
@@ -1156,13 +1156,13 @@
         <v>2.3441</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2359</v>
+        <v>-0.8254</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7125</v>
+        <v>-0.2475</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5234</v>
+        <v>-0.5779</v>
       </c>
       <c r="V9" t="n">
         <v>-2.16</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>L. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1502</v>
+        <v>-2.9636</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8077</v>
+        <v>-2.3931</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3425</v>
+        <v>-0.5705</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6863</v>
+        <v>-2.3696</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5902</v>
+        <v>-1.8985</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9039</v>
+        <v>-0.4712</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3519</v>
+        <v>-1.6063</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2827</v>
+        <v>-1.0003</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6346000000000001</v>
+        <v>-0.606</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0382</v>
+        <v>-0.7634</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3075</v>
+        <v>-0.8982</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2692</v>
+        <v>0.1348</v>
       </c>
       <c r="P10" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1721</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5265</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7705</v>
+        <v>0.3853</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2971</v>
+        <v>-0.2958</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7653</v>
+        <v>-0.488</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7653</v>
+        <v>-0.488</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. HUGUET CARRASCO</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2148</v>
+        <v>-3.2957</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4536</v>
+        <v>-2.2528</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7612</v>
+        <v>-1.0429</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3696</v>
+        <v>-0.6863</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8985</v>
+        <v>-1.5902</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4712</v>
+        <v>0.9039</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6063</v>
+        <v>0.3519</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0003</v>
+        <v>-0.2827</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.606</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7634</v>
+        <v>-1.0382</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8982</v>
+        <v>-1.3075</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1348</v>
+        <v>0.2692</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1617</v>
+        <v>-0.672</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3247</v>
+        <v>0.3255</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4865</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.488</v>
+        <v>-0.7653</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.488</v>
+        <v>-0.7653</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6027</v>
+        <v>-6.375</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5109</v>
+        <v>-4.147</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0918</v>
+        <v>-2.228</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0368</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1364</v>
+        <v>-0.9087</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4153</v>
+        <v>-0.0514</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7211</v>
+        <v>-0.8572</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4294</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.896</v>
+        <v>-10.2909</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.638400000000001</v>
+        <v>-7.033200000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-3.2577</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9556</v>
+        <v>1.955599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.465599999999999</v>
+        <v>-5.4656</v>
       </c>
       <c r="I13" t="n">
         <v>7.421000000000001</v>
@@ -1447,7 +1447,7 @@
         <v>1.8673</v>
       </c>
       <c r="L13" t="n">
-        <v>6.076800000000001</v>
+        <v>6.0768</v>
       </c>
       <c r="M13" t="n">
         <v>-5.9887</v>
@@ -1468,13 +1468,13 @@
         <v>16.6042</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.9979</v>
+        <v>-5.3927</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3841000000000003</v>
+        <v>0.2214</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.614199999999999</v>
+        <v>-5.614</v>
       </c>
       <c r="V13" t="n">
         <v>-5.876500000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>D. VIDAL TEIXIDOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7652</v>
+        <v>4.4384</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3785</v>
+        <v>3.3818</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3867</v>
+        <v>1.0566</v>
       </c>
       <c r="G14" t="n">
-        <v>2.632</v>
+        <v>0.1977</v>
       </c>
       <c r="H14" t="n">
-        <v>3.118</v>
+        <v>2.0056</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.486</v>
+        <v>-1.8079</v>
       </c>
       <c r="J14" t="n">
-        <v>3.536</v>
+        <v>1.0876</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4817</v>
+        <v>1.6807</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0543</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.904</v>
+        <v>-0.8898</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3638</v>
+        <v>0.3249</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5403</v>
+        <v>-1.2148</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3441</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6336</v>
+        <v>0.4127</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7418</v>
+        <v>0.2244</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8918</v>
+        <v>0.1883</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.1097</v>
+        <v>3.0466</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4448</v>
+        <v>3.0466</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. VIDAL TEIXIDOR</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2107</v>
+        <v>3.5685</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3706</v>
+        <v>2.2662</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8401</v>
+        <v>1.3023</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1977</v>
+        <v>2.632</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0056</v>
+        <v>3.118</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.8079</v>
+        <v>-0.486</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0876</v>
+        <v>3.536</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6807</v>
+        <v>3.4817</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0543</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8898</v>
+        <v>-0.904</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3249</v>
+        <v>-0.3638</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2148</v>
+        <v>-0.5403</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-2.3441</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8149999999999999</v>
+        <v>1.4369</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0282</v>
+        <v>0.8074</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0466</v>
+        <v>-0.1097</v>
       </c>
       <c r="W15" t="n">
-        <v>3.0466</v>
+        <v>0.4448</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8333</v>
+        <v>2.6066</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6568</v>
+        <v>1.0501</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1765</v>
+        <v>1.5565</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1592</v>
@@ -1702,13 +1702,13 @@
         <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9106</v>
+        <v>1.6839</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1187</v>
+        <v>1.512</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2081</v>
+        <v>0.1719</v>
       </c>
       <c r="V16" t="n">
         <v>0.8865</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7784</v>
+        <v>2.1043</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9786</v>
+        <v>0.1697</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7997</v>
+        <v>1.9346</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8174</v>
@@ -1780,13 +1780,13 @@
         <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>1.018</v>
+        <v>0.3439</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2025</v>
+        <v>0.3936</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1845</v>
+        <v>-0.0497</v>
       </c>
       <c r="V17" t="n">
         <v>2.9917</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. NGUBA ETAME</t>
+          <t>P. MARTINEZ ALEJANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0594</v>
+        <v>1.713</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0426</v>
+        <v>0.4262</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9832</v>
+        <v>1.2868</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9397</v>
+        <v>-0.4741</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8596</v>
+        <v>-0.3118</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0801</v>
+        <v>-0.1623</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4342</v>
+        <v>0.4249</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3533</v>
+        <v>0.4515</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>-0.0266</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4945</v>
+        <v>-0.899</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4937</v>
+        <v>-0.7634</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0008</v>
+        <v>-0.1356</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.3674</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0025</v>
+        <v>0.3824</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4213</v>
+        <v>0.1501</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4189</v>
+        <v>0.2324</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2735</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. MARTINEZ ALEJANO</t>
+          <t>D. NGUBA ETAME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8094</v>
+        <v>1.3659</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1805</v>
+        <v>2.1326</v>
       </c>
       <c r="F19" t="n">
-        <v>0.99</v>
+        <v>-0.7667</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4741</v>
+        <v>0.9397</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3118</v>
+        <v>0.8596</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1623</v>
+        <v>0.0801</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4249</v>
+        <v>1.4342</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4515</v>
+        <v>1.3533</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0266</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.899</v>
+        <v>-0.4945</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7634</v>
+        <v>-0.4937</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1356</v>
+        <v>-0.0008</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.3674</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5211</v>
+        <v>1.309</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4566</v>
+        <v>1.5113</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0645</v>
+        <v>-0.2023</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2186</v>
+        <v>-1.2735</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0.5545</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.695</v>
+        <v>0.3356</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.166</v>
+        <v>-1.0537</v>
       </c>
       <c r="F20" t="n">
-        <v>1.471</v>
+        <v>1.3893</v>
       </c>
       <c r="G20" t="n">
         <v>0.5515</v>
@@ -2014,13 +2014,13 @@
         <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.547</v>
+        <v>0.4836</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7592</v>
+        <v>0.353</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2122</v>
+        <v>0.1305</v>
       </c>
       <c r="V20" t="n">
         <v>0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3336</v>
+        <v>-0.5325</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6609</v>
+        <v>-0.7508</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3273</v>
+        <v>0.2184</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0848</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4441</v>
+        <v>0.357</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.773</v>
+        <v>0.137</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3289</v>
+        <v>0.22</v>
       </c>
       <c r="V21" t="n">
         <v>1.2186</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5318</v>
+        <v>-3.3554</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.162</v>
+        <v>-4.3643</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6303</v>
+        <v>1.0089</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7408</v>
@@ -2170,13 +2170,13 @@
         <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7605</v>
+        <v>0.9369</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9053</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1448</v>
+        <v>0.2337</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3794</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.896</v>
+        <v>12.2444</v>
       </c>
       <c r="E23" t="n">
-        <v>3.257700000000001</v>
+        <v>3.2578</v>
       </c>
       <c r="F23" t="n">
-        <v>7.638400000000001</v>
+        <v>8.986700000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9554</v>
@@ -2248,13 +2248,13 @@
         <v>17.5809</v>
       </c>
       <c r="S23" t="n">
-        <v>5.997999999999999</v>
+        <v>7.346299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>5.614000000000001</v>
+        <v>5.614</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3839</v>
+        <v>1.7322</v>
       </c>
       <c r="V23" t="n">
         <v>5.876599999999998</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484227_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484227_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.7067</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.0503</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.488</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.4418</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.488</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,11 +1379,16 @@
       <c r="X11" t="n">
         <v>-0.7653</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BENNASSAR ROSSELLÓ</t>
+          <t>A. BENNASSAR ROSSELLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1406,6 +1461,11 @@
       </c>
       <c r="X12" t="n">
         <v>-1.4294</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.258999999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>À. RIERA PERETÓ</t>
+          <t>A. RIERA PERETO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,28 +1728,28 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6066</v>
+        <v>2.2996</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0501</v>
+        <v>0.7431</v>
       </c>
       <c r="F16" t="n">
         <v>1.5565</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1592</v>
+        <v>-0.4662</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5285</v>
+        <v>0.2215</v>
       </c>
       <c r="I16" t="n">
         <v>-0.6877</v>
       </c>
       <c r="J16" t="n">
-        <v>0.605</v>
+        <v>0.298</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2919</v>
+        <v>0.9849</v>
       </c>
       <c r="L16" t="n">
         <v>-0.6869</v>
@@ -1718,6 +1789,11 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,11 +2122,16 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. PALLARES ARUMI</t>
+          <t>À. RIERA PERETÓ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5325</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7508</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2184</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0848</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2926</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7921</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7158</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.408</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.369</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1154</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4844</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LAJAY BOBEPARI</t>
+          <t>F. PALLARES ARUMI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3554</v>
+        <v>-0.5325</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3643</v>
+        <v>-0.7508</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0089</v>
+        <v>0.2184</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7408</v>
+        <v>-3.0848</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7296</v>
+        <v>-0.2926</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4704</v>
+        <v>-2.7921</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6329</v>
+        <v>-1.7158</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2931</v>
+        <v>-0.408</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6603</v>
+        <v>-1.3077</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3737</v>
+        <v>-1.369</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5636</v>
+        <v>0.1154</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8101</v>
+        <v>-1.4844</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3208</v>
+        <v>-0.3907</v>
       </c>
       <c r="R22" t="n">
-        <v>2.1488</v>
+        <v>1.3674</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9369</v>
+        <v>0.357</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.137</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2337</v>
+        <v>0.22</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3794</v>
+        <v>1.2186</v>
       </c>
       <c r="W22" t="n">
-        <v>-2.3794</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. LAJAY BOBEPARI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-3.3554</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.3643</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.0089</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.7408</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.4704</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6329</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.2931</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6603</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.3737</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.5636</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8101</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.9369</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7030999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2337</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-2.3794</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-2.3794</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484227_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. VIC - UNIVERSITAT DE VIC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>12.2444</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>3.2578</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>8.986700000000001</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-1.9554</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>5.4657</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-7.420999999999999</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>5.9888</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>7.3329</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>-1.3442</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-7.943999999999999</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-1.8675</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-6.0768</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>0.9765999999999999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>17.5809</v>
       </c>
-      <c r="S23" t="n">
-        <v>7.346299999999999</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="S24" t="n">
+        <v>7.3463</v>
+      </c>
+      <c r="T24" t="n">
         <v>5.614</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1.7322</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>5.876599999999998</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>8.2591</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-2.3824</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
